--- a/userProfile/instapay_template.xlsx
+++ b/userProfile/instapay_template.xlsx
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="D8" s="19" t="n"/>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>34+joe</t>
         </is>
@@ -1802,12 +1802,25 @@
     <row r="9" ht="15.75" customHeight="1" s="24">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Select Bank…</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="n"/>
-      <c r="C9" s="19" t="n"/>
+          <t>G-Xchange, Inc.</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Joel cruz</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>090</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="n"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>46+lilili</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="24">
       <c r="A10" s="16" t="inlineStr">
